--- a/results/simulation/tables/supp_table_coverage_titration.xlsx
+++ b/results/simulation/tables/supp_table_coverage_titration.xlsx
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="C6" t="n">
         <v>100</v>
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="C7" t="n">
         <v>100</v>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="C12" t="n">
         <v>100</v>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="C13" t="n">
         <v>100</v>
